--- a/amostras/controle/K09/matriz_rastreabilidade_K09.xlsx
+++ b/amostras/controle/K09/matriz_rastreabilidade_K09.xlsx
@@ -511,27 +511,28 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
-        </is>
-      </c>
+          <t>Nenhuma</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Amostra Não Preenchida</t>
+          <t>Nenhuma / Sem Achados</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhuma</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Aguardando geração (Passo 1 pendente)</t>
+          <t>Não se aplica (amostra limpa)</t>
         </is>
       </c>
     </row>
@@ -571,6 +572,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -628,6 +630,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -685,6 +688,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -742,6 +746,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -799,6 +804,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -856,6 +862,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -913,6 +920,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1030,6 +1038,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1087,6 +1096,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1144,6 +1154,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1201,6 +1212,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1258,6 +1270,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1315,6 +1328,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1372,6 +1386,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1429,6 +1444,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1486,6 +1502,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Nenhum</t>
